--- a/data/derived/golf_recommendations.xlsx
+++ b/data/derived/golf_recommendations.xlsx
@@ -4694,13 +4694,13 @@
         <v>216</v>
       </c>
       <c r="G111">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H111">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="I111">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J111" t="s">
         <v>43</v>
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="J112" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K112" t="s">
         <v>44</v>
@@ -4770,16 +4770,16 @@
         <v>144</v>
       </c>
       <c r="G113">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H113">
         <v>0</v>
       </c>
       <c r="I113">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J113" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K113" t="s">
         <v>44</v>
@@ -4849,10 +4849,10 @@
         <v>2</v>
       </c>
       <c r="H115">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I115">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="J115" t="s">
         <v>43</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="J116" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K116" t="s">
         <v>50</v>
@@ -4919,16 +4919,16 @@
         <v>158</v>
       </c>
       <c r="G117">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H117">
         <v>0</v>
       </c>
       <c r="I117">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J117" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K117" t="s">
         <v>47</v>
@@ -4992,13 +4992,13 @@
         <v>267</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J119" t="s">
         <v>43</v>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="J120" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K120" t="s">
         <v>44</v>
@@ -5071,13 +5071,13 @@
         <v>2</v>
       </c>
       <c r="H121">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="I121">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J121" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K121" t="s">
         <v>44</v>
@@ -5115,7 +5115,7 @@
         <v>0</v>
       </c>
       <c r="J122" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K122" t="s">
         <v>45</v>
@@ -5147,10 +5147,10 @@
         <v>0</v>
       </c>
       <c r="I123">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J123" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K123" t="s">
         <v>47</v>
@@ -5185,7 +5185,7 @@
         <v>0</v>
       </c>
       <c r="J124" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K124" t="s">
         <v>44</v>
@@ -5214,16 +5214,16 @@
         <v>135</v>
       </c>
       <c r="G125">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H125">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I125">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J125" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K125" t="s">
         <v>44</v>
@@ -5261,7 +5261,7 @@
         <v>0</v>
       </c>
       <c r="J126" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K126" t="s">
         <v>44</v>
@@ -5293,13 +5293,13 @@
         <v>2</v>
       </c>
       <c r="H127">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="I127">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J127" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K127" t="s">
         <v>44</v>
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="J128" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K128" t="s">
         <v>44</v>
@@ -5366,16 +5366,16 @@
         <v>173</v>
       </c>
       <c r="G129">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H129">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I129">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J129" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K129" t="s">
         <v>44</v>
@@ -5445,10 +5445,10 @@
         <v>2</v>
       </c>
       <c r="H131">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I131">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="J131" t="s">
         <v>43</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="I133">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="J133" t="s">
         <v>43</v>
@@ -5559,7 +5559,7 @@
         <v>0</v>
       </c>
       <c r="J134" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K134" t="s">
         <v>44</v>
@@ -5588,16 +5588,16 @@
         <v>142</v>
       </c>
       <c r="G135">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H135">
         <v>0</v>
       </c>
       <c r="I135">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J135" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K135" t="s">
         <v>44</v>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="J136" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K136" t="s">
         <v>44</v>
@@ -5664,16 +5664,16 @@
         <v>178</v>
       </c>
       <c r="G137">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I137">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J137" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K137" t="s">
         <v>44</v>
@@ -5711,7 +5711,7 @@
         <v>0</v>
       </c>
       <c r="J138" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K138" t="s">
         <v>44</v>
@@ -5740,16 +5740,16 @@
         <v>195</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H139">
         <v>0</v>
       </c>
       <c r="I139">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J139" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K139" t="s">
         <v>44</v>
@@ -5816,13 +5816,13 @@
         <v>292</v>
       </c>
       <c r="G141">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H141">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I141">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="J141" t="s">
         <v>43</v>
@@ -5889,13 +5889,13 @@
         <v>153</v>
       </c>
       <c r="G143">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H143">
         <v>0</v>
       </c>
       <c r="I143">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="J143" t="s">
         <v>43</v>
@@ -5933,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="J144" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K144" t="s">
         <v>44</v>
@@ -5965,13 +5965,13 @@
         <v>2</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I145">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J145" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K145" t="s">
         <v>44</v>

--- a/data/derived/golf_recommendations.xlsx
+++ b/data/derived/golf_recommendations.xlsx
@@ -2082,7 +2082,7 @@
         <v>198</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2155,7 +2155,7 @@
         <v>180</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="J45" t="s">
         <v>43</v>
@@ -2307,10 +2307,10 @@
         <v>2</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="J47" t="s">
         <v>43</v>
@@ -2380,10 +2380,10 @@
         <v>203</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2427,7 +2427,7 @@
         <v>0.14</v>
       </c>
       <c r="J50" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K50" t="s">
         <v>45</v>
@@ -2459,10 +2459,10 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J51" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K51" t="s">
         <v>50</v>
@@ -2526,10 +2526,10 @@
         <v>302</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2602,13 +2602,13 @@
         <v>105</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J55" t="s">
         <v>43</v>
@@ -2725,7 +2725,7 @@
         <v>0.14</v>
       </c>
       <c r="J58" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K58" t="s">
         <v>48</v>
@@ -2751,16 +2751,16 @@
         <v>187</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J59" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K59" t="s">
         <v>45</v>
@@ -2795,7 +2795,7 @@
         <v>0.14</v>
       </c>
       <c r="J60" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K60" t="s">
         <v>44</v>
@@ -2827,13 +2827,13 @@
         <v>2</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I61">
         <v>1</v>
       </c>
       <c r="J61" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K61" t="s">
         <v>44</v>
@@ -2900,13 +2900,13 @@
         <v>104</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="J63" t="s">
         <v>43</v>
@@ -2982,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="J65" t="s">
         <v>43</v>
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K66" t="s">
         <v>44</v>
@@ -3052,16 +3052,16 @@
         <v>128</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I67">
         <v>1</v>
       </c>
       <c r="J67" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K67" t="s">
         <v>44</v>
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="J69" t="s">
         <v>43</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="J71" t="s">
         <v>43</v>
@@ -3277,10 +3277,10 @@
         <v>2</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="J73" t="s">
         <v>43</v>
